--- a/Nuevo modelo/Modelo.xlsx
+++ b/Nuevo modelo/Modelo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a8e9d158fee738eb/Escritorio/01_Data science/02_Proyectos/Profesionales_personales/02_ProyectoFinanzas/Nuevo modelo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="968" documentId="11_6728A2C2DC4C5100FF52A6CD77A9E0B3E2FCC81A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A12F6B-0B52-453C-AC25-F4C9B3807E44}"/>
+  <xr:revisionPtr revIDLastSave="971" documentId="11_6728A2C2DC4C5100FF52A6CD77A9E0B3E2FCC81A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E5F91F-D50D-46F0-8C7D-E798D1BDF1EE}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2565" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FactTransaccionFinanciera" sheetId="2" r:id="rId1"/>
